--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -26794,7 +26794,7 @@
         <v>Working</v>
       </c>
       <c r="K644" t="str">
-        <v/>
+        <v>Testing</v>
       </c>
       <c r="L644" t="str">
         <v>#N/A</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -11211,10 +11211,10 @@
         <v>PATNI21-22/10467</v>
       </c>
       <c r="J264" t="str">
-        <v>Damage</v>
+        <v/>
       </c>
       <c r="K264" t="str">
-        <v/>
+        <v>given to sales team for banglore visit</v>
       </c>
       <c r="L264" t="str">
         <v>Body Damage</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -949,7 +949,7 @@
         <v>5CG0346B2F</v>
       </c>
       <c r="F14" t="str">
-        <v>Stock in Turbhe office</v>
+        <v>Palak Annawadiya</v>
       </c>
       <c r="G14" t="str">
         <v>Not Yet Assigned</v>
@@ -961,13 +961,13 @@
         <v>PATNI/20-21/8134</v>
       </c>
       <c r="J14" t="str">
-        <v>Repair Required</v>
+        <v>Working</v>
       </c>
       <c r="K14" t="str">
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Microphone Issue</v>
+        <v>Maybe Microphone Issue</v>
       </c>
       <c r="M14" t="str">
         <v>21-Jan-21</v>
@@ -11211,7 +11211,7 @@
         <v>PATNI21-22/10467</v>
       </c>
       <c r="J264" t="str">
-        <v/>
+        <v>Working</v>
       </c>
       <c r="K264" t="str">
         <v>given to sales team for banglore visit</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -11214,7 +11214,7 @@
         <v>Working</v>
       </c>
       <c r="K264" t="str">
-        <v>given to sales team for banglore visit</v>
+        <v>Anusha Badole</v>
       </c>
       <c r="L264" t="str">
         <v>Body Damage</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -8821,7 +8821,7 @@
         <v>5CG0346FQN</v>
       </c>
       <c r="F206" t="str">
-        <v>Stock in Turbhe office</v>
+        <v>Disha Pangal</v>
       </c>
       <c r="G206" t="str">
         <v>Not Yet Assigned</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -8833,7 +8833,7 @@
         <v>PATNI/20-21/7983</v>
       </c>
       <c r="J206" t="str">
-        <v>Not Working</v>
+        <v>Working</v>
       </c>
       <c r="K206" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -13044,7 +13044,7 @@
         <v>5CG1223Y30</v>
       </c>
       <c r="F309" t="str">
-        <v>Stock in Turbhe office</v>
+        <v>Suman Yadav</v>
       </c>
       <c r="G309" t="str">
         <v>Not Yet Assigned</v>
@@ -13056,13 +13056,13 @@
         <v>TS/21-22/0598</v>
       </c>
       <c r="J309" t="str">
-        <v>Repair Required</v>
+        <v>Working</v>
       </c>
       <c r="K309" t="str">
         <v/>
       </c>
       <c r="L309" t="str">
-        <v>Battery issue</v>
+        <v>Battery Replaced/Battery issue</v>
       </c>
       <c r="M309" t="str">
         <v>20-Dec-21</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -12362,7 +12362,7 @@
         <v>Available</v>
       </c>
       <c r="K292" t="str">
-        <v>Returned from Ranchna Solanki</v>
+        <v>Preshita Damahe</v>
       </c>
       <c r="L292" t="str">
         <v>spot on display</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -13454,7 +13454,7 @@
         <v>PF3P6ZDE</v>
       </c>
       <c r="F319" t="str">
-        <v>Stock in Turbhe office</v>
+        <v>Aman singh</v>
       </c>
       <c r="G319" t="str">
         <v>Not Yet Assigned</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -13466,7 +13466,7 @@
         <v>ITM2022-23/098</v>
       </c>
       <c r="J319" t="str">
-        <v>Not Working</v>
+        <v>Working</v>
       </c>
       <c r="K319" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -8792,7 +8792,7 @@
         <v>PATNI/20-21/7983</v>
       </c>
       <c r="J205" t="str">
-        <v>Not Working</v>
+        <v>Working</v>
       </c>
       <c r="K205" t="str">
         <v/>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -17308,7 +17308,7 @@
         <v>DK85RQ2</v>
       </c>
       <c r="F413" t="str">
-        <v>Kanishka Shaileshrao Kale</v>
+        <v>In Stock Turbhe</v>
       </c>
       <c r="G413" t="str">
         <v>Available</v>
@@ -17320,13 +17320,13 @@
         <v>PATNI23-24/20895</v>
       </c>
       <c r="J413" t="str">
-        <v>Working</v>
+        <v>Available</v>
       </c>
       <c r="K413" t="str">
-        <v/>
+        <v>Returned by kanishka / resigned</v>
       </c>
       <c r="L413" t="str">
-        <v>#N/A</v>
+        <v>24-10-26</v>
       </c>
       <c r="M413" t="str">
         <v>06-Apr-23</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -516,7 +516,7 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>#N/A</v>
+        <v>#N/</v>
       </c>
       <c r="M3" t="str">
         <v>29-Jun-18</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -8862,7 +8862,7 @@
         <v>5CG0346FQN</v>
       </c>
       <c r="F207" t="str">
-        <v>Disha Pangal</v>
+        <v>Gayatri Kothavle</v>
       </c>
       <c r="G207" t="str">
         <v>Not Yet Assigned</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -13085,7 +13085,7 @@
         <v>5CG1223Y30</v>
       </c>
       <c r="F310" t="str">
-        <v>Suman Yadav</v>
+        <v>Gauri Satsukar</v>
       </c>
       <c r="G310" t="str">
         <v>Not Yet Assigned</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -9884,7 +9884,7 @@
         <v>PRPL 231 HP LAPTOP</v>
       </c>
       <c r="E232" t="str">
-        <v>5CG102928W</v>
+        <v>DK85R02</v>
       </c>
       <c r="F232" t="str">
         <v>Neha Kumari Singh</v>
@@ -9899,10 +9899,10 @@
         <v>PATNI/20-21/8688</v>
       </c>
       <c r="J232" t="str">
-        <v>Working</v>
+        <v>Replaced</v>
       </c>
       <c r="K232" t="str">
-        <v/>
+        <v>Old asset S/N: 5CG102928W</v>
       </c>
       <c r="L232" t="str">
         <v>#N/A</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -11240,7 +11240,7 @@
         <v>5CG1223Y45</v>
       </c>
       <c r="F265" t="str">
-        <v>Stock in Turbhe office</v>
+        <v>Anusha Badole</v>
       </c>
       <c r="G265" t="str">
         <v>Not Yet Assigned</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -11255,7 +11255,7 @@
         <v>Working</v>
       </c>
       <c r="K265" t="str">
-        <v>Anusha Badole</v>
+        <v>Temp VC</v>
       </c>
       <c r="L265" t="str">
         <v>Body Damage</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -11199,10 +11199,10 @@
         <v>5CG1224130</v>
       </c>
       <c r="F264" t="str">
-        <v>Stock in Turbhe office</v>
+        <v>Mayuresh</v>
       </c>
       <c r="G264" t="str">
-        <v>Not Yet Assigned</v>
+        <v>Temp for Editing</v>
       </c>
       <c r="H264" t="str">
         <v>PRPL / ACQ / 16082021 / 0033</v>

--- a/IT_Asset_Inventory.xlsx
+++ b/IT_Asset_Inventory.xlsx
@@ -11211,7 +11211,7 @@
         <v>PATNI21-22/10467</v>
       </c>
       <c r="J264" t="str">
-        <v>Not Working</v>
+        <v>Working</v>
       </c>
       <c r="K264" t="str">
         <v/>
